--- a/samples/invoices-with-errors.xlsx
+++ b/samples/invoices-with-errors.xlsx
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>50000</v>
@@ -505,10 +505,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>12000</v>
@@ -527,10 +527,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>8000</v>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>-1500</v>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>9999</v>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>55000</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>12500.555</v>
